--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-aps-problems.xlsx
@@ -13,13 +13,12 @@
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
     <sheet name="Include #4" r:id="rId8" sheetId="6"/>
     <sheet name="Include #5" r:id="rId9" sheetId="7"/>
-    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -137,18 +136,6 @@
   </si>
   <si>
     <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>concept</t>
-  </si>
-  <si>
-    <t>is-a</t>
-  </si>
-  <si>
-    <t>160245001</t>
   </si>
 </sst>
 </file>
@@ -650,56 +637,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>